--- a/Blink POS Data/Blink POS Data.xlsx
+++ b/Blink POS Data/Blink POS Data.xlsx
@@ -6062,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6081,6 +6081,11 @@
           <t>website_filter</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -6096,6 +6101,11 @@
           <t>coals</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Grilled over charcoal to order. Served with naan, fresh salad, mint raita and house chutneys.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6111,6 +6121,11 @@
           <t>coals</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bold cuts, aromatic marinades and deep charcoal smoke.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6126,6 +6141,11 @@
           <t>coals</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Flavours of the river, kissed by the grill.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -6141,6 +6161,11 @@
           <t>karahi</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cooked fast, served bubbling and made for sharing.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6156,6 +6181,11 @@
           <t>karahi</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cooked slowly on the bone for full, generous flavour.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6171,6 +6201,11 @@
           <t>karahi</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Silky gravies, gentle heat and comforting richness.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6186,6 +6221,11 @@
           <t>curries</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Familiar favourites with a Flames finish.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6201,6 +6241,11 @@
           <t>curries</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Regional recipes shaped by spice, tradition and patient cooking.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6216,6 +6261,11 @@
           <t>curries</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deeply savoury, warmly spiced classics.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6231,6 +6281,11 @@
           <t>curries</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Specialities cooked patiently and served from morning into night.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6246,6 +6301,11 @@
           <t>rice</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fragrant grains layered with the flavours of the region.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6261,6 +6321,11 @@
           <t>veg</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Everyday comfort, tempered beautifully.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6276,6 +6341,11 @@
           <t>breads</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Served hot, shaped by hand and made to complete the table.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6291,6 +6361,11 @@
           <t>starters</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fresh, cool and ready to begin.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6306,6 +6381,11 @@
           <t>breakfast</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A generous start, served every morning.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6321,6 +6401,11 @@
           <t>chai</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Brewed slowly and poured hot. The heart of every gathering by the Indus.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6336,6 +6421,11 @@
           <t>chai</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Distinctive pours inspired by tea traditions across Pakistan.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6351,6 +6441,11 @@
           <t>chai</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Our own expressions of the tea ritual.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6366,6 +6461,11 @@
           <t>chai</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Summer favourites, served chilled.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6379,6 +6479,11 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>sweets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A graceful finish to the feast.</t>
         </is>
       </c>
     </row>
